--- a/data/05_modelado/results/results_lineales_ext.xlsx
+++ b/data/05_modelado/results/results_lineales_ext.xlsx
@@ -528,12 +528,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -542,63 +542,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7145404289681895</v>
+        <v>0.7498507807360217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008917274356960362</v>
+        <v>0.006027893023129959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8846695588558642</v>
+        <v>0.9080340040199995</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004505009475381636</v>
+        <v>0.003540900512979701</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7652063442951079</v>
+        <v>0.6816717829089194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6704800916999138</v>
+        <v>0.8333322562847802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8433965973968711</v>
+        <v>0.8373736705665914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.445</v>
+        <v>4.623</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7209</v>
+        <v>0.755</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8902</v>
+        <v>0.9134</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7578</v>
+        <v>0.6817</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6873</v>
+        <v>0.846</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8394</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6133</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.368</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,58 +607,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7251676987783179</v>
+        <v>0.747327937025999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00612483718205405</v>
+        <v>0.01376937941294494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8843344284988561</v>
+        <v>0.9058661087149359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004410697646695203</v>
+        <v>0.004884769542416435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6614818404456562</v>
+        <v>0.6852618333117529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8026950178157295</v>
+        <v>0.8231616598718366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8220923307009015</v>
+        <v>0.8369655157638372</v>
       </c>
       <c r="K3" t="n">
-        <v>2.828</v>
+        <v>0.764</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7287</v>
+        <v>0.7605</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8898</v>
+        <v>0.9132</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.82</v>
+        <v>0.8185</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8214</v>
+        <v>0.8492</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5981</v>
+        <v>0.6513</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4163</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -672,52 +672,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7116779433492628</v>
+        <v>0.7393836496871475</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008854312699560982</v>
+        <v>0.007832908049006399</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8823283036933158</v>
+        <v>0.9051599001258989</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004433864610869031</v>
+        <v>0.003946958430842508</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7700876878870713</v>
+        <v>0.7825349652936302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.661835807717753</v>
+        <v>0.7017556429939472</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8432479607118694</v>
+        <v>0.8552946160581802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.525</v>
+        <v>0.822</v>
       </c>
       <c r="L4" t="n">
-        <v>5.14</v>
+        <v>6.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7205</v>
+        <v>0.7494</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8887</v>
+        <v>0.9069</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7651</v>
+        <v>0.8022</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6807</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8455</v>
+        <v>0.8625</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6142</v>
+        <v>0.6552</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3681</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="5">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7131382162666238</v>
+        <v>0.7359116552775953</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003093239870022109</v>
+        <v>0.007200138561096124</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8741241306358422</v>
+        <v>0.9038660096861791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005511197211547377</v>
+        <v>0.00580205681122376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6465284319982184</v>
+        <v>0.6491643590957055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7962127741728066</v>
+        <v>0.849860858790049</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8126486107684366</v>
+        <v>0.821571559783296</v>
       </c>
       <c r="K5" t="n">
-        <v>4.999</v>
+        <v>3.093</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7187</v>
+        <v>0.7337</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8861</v>
+        <v>0.9001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6777</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8119</v>
+        <v>0.7997</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8141</v>
+        <v>0.8302</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5826</v>
+        <v>0.6103</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8823</v>
+        <v>0.6812</v>
       </c>
     </row>
     <row r="6">
@@ -802,52 +802,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6941913512113745</v>
+        <v>0.7267192283247618</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01006942602794927</v>
+        <v>0.01577460752560449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8661494164195437</v>
+        <v>0.8997149781030049</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00671958876914109</v>
+        <v>0.004231156829102635</v>
       </c>
       <c r="H6" t="n">
-        <v>0.730478335432205</v>
+        <v>0.7864884931006975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6628575767538456</v>
+        <v>0.6805268544554671</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8294168772819536</v>
+        <v>0.8509814845146796</v>
       </c>
       <c r="K6" t="n">
-        <v>5.234</v>
+        <v>18.532</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7084</v>
+        <v>0.7271</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8783</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7476</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6731</v>
+        <v>0.6914</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8379</v>
+        <v>0.8482</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5966</v>
+        <v>0.6223</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.7409</v>
       </c>
     </row>
     <row r="7">
@@ -867,52 +867,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6959085906644356</v>
+        <v>0.7261581011517647</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01949689649156733</v>
+        <v>0.01875638316318416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.863202763096637</v>
+        <v>0.8904495092967712</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01055555723602859</v>
+        <v>0.0127432871352812</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6248996621655765</v>
+        <v>0.6575439998429703</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7878241545909329</v>
+        <v>0.8189757914489345</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7979611472675993</v>
+        <v>0.8190070569079394</v>
       </c>
       <c r="K7" t="n">
-        <v>5.38</v>
+        <v>2.54</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6918</v>
+        <v>0.7156</v>
       </c>
       <c r="N7" t="n">
-        <v>0.87</v>
+        <v>0.8931</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.6206</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7931</v>
+        <v>0.8449</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7933</v>
+        <v>0.8036</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5401</v>
+        <v>0.5709</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2521</v>
+        <v>0.8991</v>
       </c>
     </row>
     <row r="8">
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,52 +932,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5867712130180907</v>
+        <v>0.7158664191688076</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03591590599266724</v>
+        <v>0.00986043738027908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8488396124380351</v>
+        <v>0.8832410336398798</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008353262699786791</v>
+        <v>0.007139590517034026</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8153247288753673</v>
+        <v>0.6531384758078419</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4600861423432753</v>
+        <v>0.7923979220502264</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8115336524871954</v>
+        <v>0.8160317315513794</v>
       </c>
       <c r="K8" t="n">
-        <v>5.942</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>5.32</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4452</v>
+        <v>0.7274</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8433</v>
+        <v>0.8915</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7376</v>
+        <v>0.6519</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3188</v>
+        <v>0.8226</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8196</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3262</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4671</v>
+        <v>0.4494</v>
       </c>
     </row>
     <row r="9">
@@ -997,52 +997,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4857065282087784</v>
+        <v>0.6319948658525671</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03844693262637554</v>
+        <v>0.0390039191867483</v>
       </c>
       <c r="F9" t="n">
-        <v>0.848525965825041</v>
+        <v>0.869424006109857</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004987952975853188</v>
+        <v>0.0218725251244608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7984896368776917</v>
+        <v>0.7954658103754625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3517710313251493</v>
+        <v>0.5260559585960995</v>
       </c>
       <c r="J9" t="n">
-        <v>0.783611276401205</v>
+        <v>0.8214975628062042</v>
       </c>
       <c r="K9" t="n">
-        <v>6.822</v>
+        <v>8.106</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4648</v>
+        <v>0.4465</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8502</v>
+        <v>0.8597</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7408</v>
+        <v>0.716</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3386</v>
+        <v>0.3244</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7719</v>
+        <v>0.7648</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3445</v>
+        <v>0.323</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4769</v>
+        <v>0.4591</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6701084643253468</v>
+        <v>0.6224816539270621</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02069116428210701</v>
+        <v>0.04430817190313216</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8426267344924778</v>
+        <v>0.8692919612377658</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01293406320725295</v>
+        <v>0.009158002606966488</v>
       </c>
       <c r="H10" t="n">
-        <v>0.599996685635648</v>
+        <v>0.8075223176092313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7598566502228279</v>
+        <v>0.5100422391516304</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7809721061736022</v>
+        <v>0.8206423576195739</v>
       </c>
       <c r="K10" t="n">
-        <v>5.913</v>
+        <v>5.042</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6731</v>
+        <v>0.5841</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8339</v>
+        <v>0.855</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6014</v>
+        <v>0.7534</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7641</v>
+        <v>0.4769</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7829</v>
+        <v>0.8013</v>
       </c>
       <c r="R10" t="n">
-        <v>0.514</v>
+        <v>0.4621</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5302</v>
+        <v>0.4427</v>
       </c>
     </row>
   </sheetData>
